--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">Product</t>
   </si>
@@ -73,28 +73,16 @@
     <t xml:space="preserve">Animares</t>
   </si>
   <si>
-    <t xml:space="preserve">Xtour</t>
-  </si>
-  <si>
     <t xml:space="preserve">Others</t>
   </si>
   <si>
     <t xml:space="preserve">BBQ</t>
   </si>
   <si>
-    <t xml:space="preserve">Wineglass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bar 2024</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lollipop</t>
   </si>
   <si>
     <t xml:space="preserve">Car rental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FF</t>
   </si>
 </sst>
 </file>
@@ -109,6 +97,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -129,6 +118,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -173,16 +163,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -309,7 +303,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1000"/>
+  <dimension ref="A1:B996"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -324,7 +318,7 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -332,7 +326,7 @@
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -340,169 +334,141 @@
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>3</v>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>1</v>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>2</v>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>3</v>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>4</v>
+      <c r="B8" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>5</v>
+      <c r="B9" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>6</v>
+      <c r="B10" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>7</v>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>8</v>
+      <c r="B12" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>9</v>
+      <c r="B13" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>10</v>
+      <c r="B14" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="0" t="n">
-        <v>11</v>
+      <c r="B15" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="0" t="n">
-        <v>12</v>
-      </c>
+      <c r="B16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="0" t="n">
-        <v>13</v>
-      </c>
+      <c r="B17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="0" t="n">
-        <v>14</v>
-      </c>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="0" t="n">
-        <v>15</v>
+      <c r="B19" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="0" t="n">
-        <v>16</v>
-      </c>
+      <c r="B20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>17</v>
-      </c>
+      <c r="A21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>18</v>
-      </c>
+      <c r="A22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>19</v>
-      </c>
+      <c r="A23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>20</v>
-      </c>
+      <c r="A24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -3419,18 +3385,6 @@
     </row>
     <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A996" s="2"/>
-    </row>
-    <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A997" s="2"/>
-    </row>
-    <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A998" s="2"/>
-    </row>
-    <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A999" s="2"/>
-    </row>
-    <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
